--- a/plantillas/encuestas/plantilla-encuesta-mdeia-docente.xlsx
+++ b/plantillas/encuestas/plantilla-encuesta-mdeia-docente.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -521,130 +521,142 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>META_SEDE</t>
+          <t>Unidades MDeIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>¿En qué sede desarrollás principalmente tu actividad docente? [meta_sede]</t>
+          <t>Departamento Administrativo Sede San Juan; Departamento Administrativo Sede San Luis; ECRyPSJ- Escuela de Cultura Religiosa y Pastoral Sede San Juan; ESEGSJ- Escuela de Seguridad Sede San Juan; FBOSCO- Facultad Don Bosco Sede Mendoza; FCEESJ- Facultad de Ciencias Económicas y Empresariales Sede San Juan; FCEESL- Facultad de Ciencias Económicas y Empresariales Sede San Luis; FCMSJ- Facultad de Ciencias Médicas Sede San Juan; FCMSL- Facultad de Ciencias Médicas Sede San Luis; FCQyTSJ- Facultad de Ciencias Químicas y Tecnológicas Sede San Juan; FCVSL- Facultad de Ciencias Veterinarias Sede San Luis; FDCSSJ- Facultad de Derecho y Ciencias Sociales Sede San Juan; FDCSSL- Facultad de Derecho y Ciencias Sociales Sede San Luis; FFyHSJ- Facultad de Filosofía y Humanidades Sede San Juan; ISB- Instituto de Formación Docente San Buenaventura Sede San Juan; ISDSM- Instituto de Formación Docente Santa María Sede San Juan; OIA- Observatorio de Inteligencia Artificial; Secretaría de Extensión; Secretaría de Investigación; UCCuyo — Universidad Católica de Cuyo (institución completa)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>META_UNIDAD</t>
+          <t>META_SEDE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Facultad o departamento académico [texto]</t>
+          <t>¿En qué sede desarrollás principalmente tu actividad docente? [meta_sede]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IND_FORM_IA__recibida</t>
+          <t>META_UNIDAD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>¿Qué nivel de formación formal recibiste sobre IA aplicada a la docencia? [madurez]</t>
+          <t>Facultad o departamento académico (lista oficial MDeIA UCCuyo) [meta_unidad]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IND_IA_USO__planificacion</t>
+          <t>IND_FORM_IA__recibida</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>¿Con qué frecuencia usás IA para planificar clases, materiales o rúbricas? [frecuencia]</t>
+          <t>¿Qué nivel de formación formal recibiste sobre IA aplicada a la docencia? [madurez]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IND_IA_USO__evaluacion</t>
+          <t>IND_IA_USO__planificacion</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>¿Con qué frecuencia usás IA en el diseño o corrección de evaluaciones? [frecuencia]</t>
+          <t>¿Con qué frecuencia usás IA para planificar clases, materiales o rúbricas? [frecuencia]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IND_INTEGRIDAD__guia_catedra</t>
+          <t>IND_IA_USO__evaluacion</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>¿Tu cátedra cuenta con guía explícita de integridad académica que contempla el uso de IA? [si_no_elaboracion]</t>
+          <t>¿Con qué frecuencia usás IA en el diseño o corrección de evaluaciones? [frecuencia]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IND_EVAL_AUTENTICA__practicas</t>
+          <t>IND_INTEGRIDAD__guia_catedra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>¿En qué nivel implementás evaluaciones auténticas que reducen la dependencia de IA no declarada? [madurez]</t>
+          <t>¿Tu cátedra cuenta con guía explícita de integridad académica que contempla el uso de IA? [si_no_elaboracion]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IND_GUIA_ETICA__conocimiento</t>
+          <t>IND_EVAL_AUTENTICA__practicas</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>¿Conocés y aplicás la guía institucional de uso responsable de IA generativa? [madurez]</t>
+          <t>¿En qué nivel implementás evaluaciones auténticas que reducen la dependencia de IA no declarada? [madurez]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IND_LMS__uso_avanzado</t>
+          <t>IND_GUIA_ETICA__conocimiento</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>¿En qué nivel usás funcionalidades avanzadas del LMS (foros, entregas, videoclase, analítica)? [madurez]</t>
+          <t>¿Conocés y aplicás la guía institucional de uso responsable de IA generativa? [madurez]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IND_ALFABETIZACION__aplicacion</t>
+          <t>IND_LMS__uso_avanzado</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>¿En qué nivel incorporás alfabetización algorítmica y pedagogía con IA en tu práctica docente? [madurez]</t>
+          <t>¿En qué nivel usás funcionalidades avanzadas del LMS (foros, entregas, videoclase, analítica)? [madurez]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>IND_ALFABETIZACION__aplicacion</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>¿En qué nivel incorporás alfabetización algorítmica y pedagogía con IA en tu práctica docente? [madurez]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>IND_COMINNOVA__conocimiento</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>¿Conocés las recomendaciones de la Comisión de Innovación Docente sobre nuevas tecnologías? [si_no]</t>
         </is>
